--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Airflow Architecture/airflow_architecture_questions.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Airflow Architecture/airflow_architecture_questions.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airflow Architecture" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>Explanation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>The four main components are Scheduler, Webserver, Worker, and Metadata Database.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The four main components are Scheduler, Webserver, Worker, and Metadata Database.</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -481,15 +481,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Orchestration</t>
+          <t>The scheduler triggers DAGs and submits tasks to the executor.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The scheduler triggers DAGs and submits tasks to the executor.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -504,15 +503,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Webserver</t>
+          <t>The webserver serves the web interface for monitoring.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The webserver serves the web interface for monitoring.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -527,15 +525,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Metadata DB</t>
+          <t>The metadata database stores DAG runs, task instances, and variables.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The metadata database stores DAG runs, task instances, and variables.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -557,12 +554,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>The executor determines how tasks are executed (local, distributed, etc.).</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The executor determines how tasks are executed (local, distributed, etc.).</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -577,15 +574,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CeleryExecutor</t>
+          <t>CeleryExecutor enables distributed task execution.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CeleryExecutor enables distributed task execution.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -600,15 +596,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Task distribution</t>
+          <t>The queue distributes tasks to worker processes.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The queue distributes tasks to worker processes.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -623,15 +618,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Execute tasks</t>
+          <t>Workers are processes that actually execute the tasks.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Workers are processes that actually execute the tasks.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -646,15 +640,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Scheduler</t>
+          <t>The scheduler parses DAG files to understand workflows.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The scheduler parses DAG files to understand workflows.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -669,15 +662,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>dags_folder</t>
+          <t>This directory contains all DAG definition files.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>This directory contains all DAG definition files.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -699,12 +691,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>DAG files must be in the configured dags_folder.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DAG files must be in the configured dags_folder.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -719,15 +711,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Parallelism</t>
+          <t>LocalExecutor supports parallelism; SequentialExecutor runs one task at a time.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LocalExecutor supports parallelism; SequentialExecutor runs one task at a time.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -742,15 +733,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>The webserver default port is 8080.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The webserver default port is 8080.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -765,15 +755,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Scheduler</t>
+          <t>The scheduler manages retry logic for failed tasks.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The scheduler manages retry logic for failed tasks.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -788,15 +777,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>State storage</t>
+          <t>The database stores the state of each task instance.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The database stores the state of each task instance.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -818,12 +806,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>High availability requires multiple nodes and HA database.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>High availability requires multiple nodes and HA database.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -838,15 +826,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Async tasks</t>
+          <t>The triggerer handles deferrable operators and async tasks.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>The triggerer handles deferrable operators and async tasks.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -861,15 +848,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Message broker</t>
+          <t>Using Redis or RabbitMQ as a message broker.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Using Redis or RabbitMQ as a message broker.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -884,15 +870,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No scheduling</t>
+          <t>New DAG runs won't be scheduled until it restarts.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>New DAG runs won't be scheduled until it restarts.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -907,15 +892,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Metrics</t>
+          <t>Statsd collects and sends metrics for monitoring.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Statsd collects and sends metrics for monitoring.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
